--- a/Team-Data/2008-09/2-22-2008-09.xlsx
+++ b/Team-Data/2008-09/2-22-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -757,7 +824,7 @@
         <v>22</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK2" t="n">
         <v>14</v>
@@ -772,10 +839,10 @@
         <v>14</v>
       </c>
       <c r="AO2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AP2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ2" t="n">
         <v>29</v>
@@ -787,16 +854,16 @@
         <v>19</v>
       </c>
       <c r="AT2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
         <v>19</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -858,49 +925,49 @@
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.5</v>
+        <v>37.3</v>
       </c>
       <c r="J3" t="n">
         <v>77.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.486</v>
+        <v>0.483</v>
       </c>
       <c r="L3" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M3" t="n">
         <v>16.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.387</v>
+        <v>0.383</v>
       </c>
       <c r="O3" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="P3" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.775</v>
+        <v>0.773</v>
       </c>
       <c r="R3" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S3" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T3" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U3" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="W3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X3" t="n">
         <v>4.8</v>
@@ -909,16 +976,16 @@
         <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="AA3" t="n">
         <v>22.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.7</v>
+        <v>101</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="AD3" t="n">
         <v>5</v>
@@ -945,7 +1012,7 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM3" t="n">
         <v>20</v>
@@ -954,19 +1021,19 @@
         <v>4</v>
       </c>
       <c r="AO3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ3" t="n">
         <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
         <v>6</v>
@@ -981,7 +1048,7 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -993,7 +1060,7 @@
         <v>6</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -1025,37 +1092,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E4" t="n">
         <v>22</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>0.393</v>
+        <v>0.4</v>
       </c>
       <c r="H4" t="n">
         <v>48.7</v>
       </c>
       <c r="I4" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="J4" t="n">
-        <v>76.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.447</v>
+        <v>0.449</v>
       </c>
       <c r="L4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="M4" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0.361</v>
+        <v>0.364</v>
       </c>
       <c r="O4" t="n">
         <v>17.9</v>
@@ -1064,7 +1131,7 @@
         <v>24.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.739</v>
+        <v>0.737</v>
       </c>
       <c r="R4" t="n">
         <v>10.8</v>
@@ -1076,34 +1143,34 @@
         <v>39.5</v>
       </c>
       <c r="U4" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V4" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="W4" t="n">
         <v>7</v>
       </c>
       <c r="X4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y4" t="n">
         <v>6.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA4" t="n">
         <v>21.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>92.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.1</v>
+        <v>-1.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
         <v>22</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>24</v>
@@ -1133,10 +1200,10 @@
         <v>23</v>
       </c>
       <c r="AN4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP4" t="n">
         <v>20</v>
@@ -1154,22 +1221,22 @@
         <v>25</v>
       </c>
       <c r="AU4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV4" t="n">
         <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA4" t="n">
         <v>14</v>
@@ -1178,7 +1245,7 @@
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -1210,28 +1277,28 @@
         <v>55</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>0.436</v>
+        <v>0.455</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M5" t="n">
         <v>15.8</v>
@@ -1240,58 +1307,58 @@
         <v>0.377</v>
       </c>
       <c r="O5" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="P5" t="n">
-        <v>24.3</v>
+        <v>24.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.79</v>
+        <v>0.791</v>
       </c>
       <c r="R5" t="n">
         <v>12</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="T5" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U5" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V5" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W5" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y5" t="n">
         <v>5.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.5</v>
+        <v>100.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.6</v>
+        <v>-1.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
         <v>18</v>
@@ -1306,7 +1373,7 @@
         <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL5" t="n">
         <v>22</v>
@@ -1315,13 +1382,13 @@
         <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1333,7 +1400,7 @@
         <v>14</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
         <v>12</v>
@@ -1342,7 +1409,7 @@
         <v>24</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX5" t="n">
         <v>4</v>
@@ -1354,7 +1421,7 @@
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB5" t="n">
         <v>12</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -1392,88 +1459,88 @@
         <v>53</v>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.792</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J6" t="n">
-        <v>78.5</v>
+        <v>78.3</v>
       </c>
       <c r="K6" t="n">
         <v>0.475</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
         <v>20.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0.388</v>
+        <v>0.383</v>
       </c>
       <c r="O6" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P6" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.752</v>
+        <v>0.751</v>
       </c>
       <c r="R6" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S6" t="n">
         <v>31.1</v>
       </c>
       <c r="T6" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U6" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V6" t="n">
-        <v>12.9</v>
+        <v>13.2</v>
       </c>
       <c r="W6" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y6" t="n">
         <v>3.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.2</v>
+        <v>100.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE6" t="n">
         <v>3</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
         <v>2</v>
@@ -1485,25 +1552,25 @@
         <v>10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
         <v>5</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM6" t="n">
         <v>4</v>
       </c>
       <c r="AN6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>23</v>
@@ -1515,31 +1582,31 @@
         <v>10</v>
       </c>
       <c r="AT6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU6" t="n">
         <v>24</v>
       </c>
       <c r="AV6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AW6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
         <v>4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BA6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>1.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>9</v>
@@ -1679,7 +1746,7 @@
         <v>11</v>
       </c>
       <c r="AN7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO7" t="n">
         <v>25</v>
@@ -1694,7 +1761,7 @@
         <v>14</v>
       </c>
       <c r="AS7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT7" t="n">
         <v>7</v>
@@ -1718,10 +1785,10 @@
         <v>3</v>
       </c>
       <c r="BA7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E8" t="n">
         <v>37</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>0.661</v>
+        <v>0.673</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
@@ -1771,7 +1838,7 @@
         <v>37</v>
       </c>
       <c r="J8" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K8" t="n">
         <v>0.472</v>
@@ -1783,31 +1850,31 @@
         <v>17.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O8" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="P8" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.758</v>
+        <v>0.756</v>
       </c>
       <c r="R8" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S8" t="n">
         <v>30.5</v>
       </c>
       <c r="T8" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U8" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="V8" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="W8" t="n">
         <v>9.1</v>
@@ -1816,22 +1883,22 @@
         <v>5.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.6</v>
+        <v>103.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1849,7 +1916,7 @@
         <v>11</v>
       </c>
       <c r="AJ8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1861,10 +1928,10 @@
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP8" t="n">
         <v>1</v>
@@ -1879,13 +1946,13 @@
         <v>12</v>
       </c>
       <c r="AT8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1897,16 +1964,16 @@
         <v>27</v>
       </c>
       <c r="AZ8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB8" t="n">
         <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -1935,88 +2002,88 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E9" t="n">
         <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.509</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J9" t="n">
-        <v>79.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.453</v>
+        <v>0.455</v>
       </c>
       <c r="L9" t="n">
         <v>4.6</v>
       </c>
       <c r="M9" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O9" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P9" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.744</v>
+        <v>0.745</v>
       </c>
       <c r="R9" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T9" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U9" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V9" t="n">
         <v>12.1</v>
       </c>
       <c r="W9" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X9" t="n">
         <v>4.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>93.2</v>
+        <v>93.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>-1</v>
+        <v>-0.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AE9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF9" t="n">
         <v>15</v>
@@ -2028,7 +2095,7 @@
         <v>12</v>
       </c>
       <c r="AI9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AJ9" t="n">
         <v>19</v>
@@ -2043,7 +2110,7 @@
         <v>28</v>
       </c>
       <c r="AN9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO9" t="n">
         <v>29</v>
@@ -2052,16 +2119,16 @@
         <v>27</v>
       </c>
       <c r="AQ9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AS9" t="n">
         <v>16</v>
       </c>
       <c r="AT9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU9" t="n">
         <v>23</v>
@@ -2073,16 +2140,16 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AY9" t="n">
         <v>6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB9" t="n">
         <v>29</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -2225,10 +2292,10 @@
         <v>17</v>
       </c>
       <c r="AN10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP10" t="n">
         <v>2</v>
@@ -2243,10 +2310,10 @@
         <v>15</v>
       </c>
       <c r="AT10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV10" t="n">
         <v>19</v>
@@ -2264,13 +2331,13 @@
         <v>22</v>
       </c>
       <c r="BA10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB10" t="n">
         <v>2</v>
       </c>
       <c r="BC10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F11" t="n">
         <v>21</v>
       </c>
       <c r="G11" t="n">
-        <v>0.625</v>
+        <v>0.618</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
@@ -2317,37 +2384,37 @@
         <v>35.5</v>
       </c>
       <c r="J11" t="n">
-        <v>79.7</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L11" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M11" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.379</v>
+        <v>0.377</v>
       </c>
       <c r="O11" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="P11" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R11" t="n">
         <v>10.9</v>
       </c>
       <c r="S11" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T11" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U11" t="n">
         <v>20.5</v>
@@ -2356,13 +2423,13 @@
         <v>14.3</v>
       </c>
       <c r="W11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="X11" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z11" t="n">
         <v>18.9</v>
@@ -2371,13 +2438,13 @@
         <v>20.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
@@ -2392,22 +2459,22 @@
         <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ11" t="n">
         <v>16</v>
       </c>
       <c r="AK11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM11" t="n">
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO11" t="n">
         <v>11</v>
@@ -2419,28 +2486,28 @@
         <v>4</v>
       </c>
       <c r="AR11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="n">
         <v>19</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AX11" t="n">
         <v>28</v>
       </c>
       <c r="AY11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ11" t="n">
         <v>2</v>
@@ -2452,7 +2519,7 @@
         <v>18</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -2481,37 +2548,37 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F12" t="n">
         <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>0.414</v>
+        <v>0.404</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
       </c>
       <c r="I12" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="J12" t="n">
         <v>86</v>
       </c>
       <c r="K12" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L12" t="n">
         <v>7.8</v>
       </c>
       <c r="M12" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.372</v>
+        <v>0.37</v>
       </c>
       <c r="O12" t="n">
         <v>19.1</v>
@@ -2523,49 +2590,49 @@
         <v>0.806</v>
       </c>
       <c r="R12" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S12" t="n">
         <v>32.2</v>
       </c>
       <c r="T12" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="U12" t="n">
         <v>22.5</v>
       </c>
       <c r="V12" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W12" t="n">
         <v>6.9</v>
       </c>
       <c r="X12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y12" t="n">
         <v>5.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.6</v>
+        <v>104.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG12" t="n">
         <v>21</v>
@@ -2583,7 +2650,7 @@
         <v>17</v>
       </c>
       <c r="AL12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM12" t="n">
         <v>3</v>
@@ -2592,7 +2659,7 @@
         <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP12" t="n">
         <v>21</v>
@@ -2616,7 +2683,7 @@
         <v>22</v>
       </c>
       <c r="AW12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -2625,7 +2692,7 @@
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA12" t="n">
         <v>11</v>
@@ -2634,7 +2701,7 @@
         <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -2663,46 +2730,46 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E13" t="n">
         <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>0.232</v>
+        <v>0.236</v>
       </c>
       <c r="H13" t="n">
         <v>48.6</v>
       </c>
       <c r="I13" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="J13" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.434</v>
+        <v>0.436</v>
       </c>
       <c r="L13" t="n">
         <v>6.3</v>
       </c>
       <c r="M13" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O13" t="n">
         <v>17.1</v>
       </c>
       <c r="P13" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.749</v>
+        <v>0.751</v>
       </c>
       <c r="R13" t="n">
         <v>11.3</v>
@@ -2711,10 +2778,10 @@
         <v>28.8</v>
       </c>
       <c r="T13" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="U13" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V13" t="n">
         <v>14.8</v>
@@ -2726,22 +2793,22 @@
         <v>6.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AA13" t="n">
         <v>19.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="AC13" t="n">
-        <v>-8.9</v>
+        <v>-8.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
@@ -2753,10 +2820,10 @@
         <v>27</v>
       </c>
       <c r="AH13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ13" t="n">
         <v>8</v>
@@ -2771,13 +2838,13 @@
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO13" t="n">
         <v>27</v>
       </c>
       <c r="AP13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ13" t="n">
         <v>24</v>
@@ -2789,28 +2856,28 @@
         <v>25</v>
       </c>
       <c r="AT13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW13" t="n">
         <v>23</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>20</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
       </c>
       <c r="AY13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -2860,43 +2927,43 @@
         <v>48.4</v>
       </c>
       <c r="I14" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="J14" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.478</v>
+        <v>0.477</v>
       </c>
       <c r="L14" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M14" t="n">
         <v>18.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.367</v>
+        <v>0.37</v>
       </c>
       <c r="O14" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="P14" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.768</v>
+        <v>0.769</v>
       </c>
       <c r="R14" t="n">
         <v>12.7</v>
       </c>
       <c r="S14" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T14" t="n">
-        <v>44.5</v>
+        <v>44.8</v>
       </c>
       <c r="U14" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="V14" t="n">
         <v>13.6</v>
@@ -2905,7 +2972,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y14" t="n">
         <v>4.6</v>
@@ -2914,16 +2981,16 @@
         <v>20.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AB14" t="n">
-        <v>109.2</v>
+        <v>108.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2944,7 +3011,7 @@
         <v>4</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>11</v>
@@ -2953,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
         <v>5</v>
@@ -2962,13 +3029,13 @@
         <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2989,7 +3056,7 @@
         <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3117,7 +3184,7 @@
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI15" t="n">
         <v>29</v>
@@ -3126,7 +3193,7 @@
         <v>27</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL15" t="n">
         <v>28</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E16" t="n">
         <v>29</v>
       </c>
       <c r="F16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>0.527</v>
+        <v>0.537</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3227,19 +3294,19 @@
         <v>36.4</v>
       </c>
       <c r="J16" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K16" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L16" t="n">
         <v>6.8</v>
       </c>
       <c r="M16" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O16" t="n">
         <v>16.9</v>
@@ -3248,22 +3315,22 @@
         <v>22.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.747</v>
+        <v>0.744</v>
       </c>
       <c r="R16" t="n">
         <v>10.1</v>
       </c>
       <c r="S16" t="n">
-        <v>28.9</v>
+        <v>29.1</v>
       </c>
       <c r="T16" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="U16" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V16" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="W16" t="n">
         <v>8.1</v>
@@ -3281,13 +3348,13 @@
         <v>19.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>96.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.3</v>
+        <v>0.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3317,16 +3384,16 @@
         <v>10</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
         <v>28</v>
       </c>
       <c r="AP16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AQ16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AR16" t="n">
         <v>24</v>
@@ -3335,7 +3402,7 @@
         <v>24</v>
       </c>
       <c r="AT16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU16" t="n">
         <v>26</v>
@@ -3347,22 +3414,22 @@
         <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY16" t="n">
         <v>5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB16" t="n">
         <v>23</v>
       </c>
       <c r="BC16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -3394,13 +3461,13 @@
         <v>58</v>
       </c>
       <c r="E17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G17" t="n">
-        <v>0.483</v>
+        <v>0.466</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3409,64 +3476,64 @@
         <v>36.6</v>
       </c>
       <c r="J17" t="n">
-        <v>81.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="K17" t="n">
         <v>0.45</v>
       </c>
       <c r="L17" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M17" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.362</v>
+        <v>0.361</v>
       </c>
       <c r="O17" t="n">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="P17" t="n">
-        <v>26.6</v>
+        <v>26.2</v>
       </c>
       <c r="Q17" t="n">
         <v>0.781</v>
       </c>
       <c r="R17" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="T17" t="n">
         <v>41.3</v>
       </c>
       <c r="U17" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V17" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W17" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X17" t="n">
         <v>3.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z17" t="n">
         <v>23.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3475,7 +3542,7 @@
         <v>15</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
@@ -3484,7 +3551,7 @@
         <v>18</v>
       </c>
       <c r="AI17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ17" t="n">
         <v>11</v>
@@ -3496,13 +3563,13 @@
         <v>23</v>
       </c>
       <c r="AM17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP17" t="n">
         <v>7</v>
@@ -3517,13 +3584,13 @@
         <v>23</v>
       </c>
       <c r="AT17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU17" t="n">
         <v>10</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
         <v>15</v>
@@ -3535,7 +3602,7 @@
         <v>12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA17" t="n">
         <v>4</v>
@@ -3544,7 +3611,7 @@
         <v>13</v>
       </c>
       <c r="BC17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -3573,64 +3640,64 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E18" t="n">
         <v>18</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G18" t="n">
-        <v>0.327</v>
+        <v>0.333</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
       </c>
       <c r="I18" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J18" t="n">
         <v>83.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L18" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M18" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="N18" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O18" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P18" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q18" t="n">
         <v>0.766</v>
       </c>
       <c r="R18" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S18" t="n">
         <v>29.8</v>
       </c>
       <c r="T18" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U18" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V18" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W18" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X18" t="n">
         <v>4.1</v>
@@ -3645,19 +3712,19 @@
         <v>20.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>99.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC18" t="n">
         <v>-3.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
       </c>
       <c r="AF18" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG18" t="n">
         <v>25</v>
@@ -3666,7 +3733,7 @@
         <v>9</v>
       </c>
       <c r="AI18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ18" t="n">
         <v>5</v>
@@ -3681,10 +3748,10 @@
         <v>16</v>
       </c>
       <c r="AN18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP18" t="n">
         <v>14</v>
@@ -3696,19 +3763,19 @@
         <v>4</v>
       </c>
       <c r="AS18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU18" t="n">
         <v>21</v>
       </c>
       <c r="AV18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX18" t="n">
         <v>25</v>
@@ -3720,10 +3787,10 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -3836,10 +3903,10 @@
         <v>5</v>
       </c>
       <c r="AE19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG19" t="n">
         <v>19</v>
@@ -3866,10 +3933,10 @@
         <v>10</v>
       </c>
       <c r="AO19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ19" t="n">
         <v>12</v>
@@ -3890,7 +3957,7 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX19" t="n">
         <v>20</v>
@@ -3899,7 +3966,7 @@
         <v>17</v>
       </c>
       <c r="AZ19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA19" t="n">
         <v>19</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
         <v>11</v>
@@ -4036,7 +4103,7 @@
         <v>29</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>9</v>
@@ -4045,7 +4112,7 @@
         <v>9</v>
       </c>
       <c r="AN20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO20" t="n">
         <v>21</v>
@@ -4090,7 +4157,7 @@
         <v>25</v>
       </c>
       <c r="BC20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E21" t="n">
         <v>23</v>
       </c>
       <c r="F21" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G21" t="n">
-        <v>0.418</v>
+        <v>0.426</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
@@ -4137,7 +4204,7 @@
         <v>38.6</v>
       </c>
       <c r="J21" t="n">
-        <v>86.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="K21" t="n">
         <v>0.445</v>
@@ -4146,19 +4213,19 @@
         <v>10.4</v>
       </c>
       <c r="M21" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="N21" t="n">
-        <v>0.361</v>
+        <v>0.36</v>
       </c>
       <c r="O21" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P21" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="R21" t="n">
         <v>10.9</v>
@@ -4173,7 +4240,7 @@
         <v>21.8</v>
       </c>
       <c r="V21" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W21" t="n">
         <v>7.1</v>
@@ -4182,28 +4249,28 @@
         <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA21" t="n">
         <v>19.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>105.5</v>
+        <v>105.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.1</v>
+        <v>-1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
         <v>20</v>
@@ -4218,10 +4285,10 @@
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM21" t="n">
         <v>1</v>
@@ -4230,7 +4297,7 @@
         <v>20</v>
       </c>
       <c r="AO21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP21" t="n">
         <v>28</v>
@@ -4242,25 +4309,25 @@
         <v>15</v>
       </c>
       <c r="AS21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU21" t="n">
         <v>8</v>
       </c>
       <c r="AV21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW21" t="n">
         <v>17</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>16</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ21" t="n">
         <v>6</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -4385,22 +4452,22 @@
         <v>27</v>
       </c>
       <c r="AF22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH22" t="n">
         <v>16</v>
       </c>
       <c r="AI22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
       </c>
       <c r="AK22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="n">
         <v>30</v>
@@ -4409,13 +4476,13 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO22" t="n">
         <v>8</v>
       </c>
       <c r="AP22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ22" t="n">
         <v>11</v>
@@ -4427,22 +4494,22 @@
         <v>11</v>
       </c>
       <c r="AT22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX22" t="n">
         <v>21</v>
       </c>
       <c r="AY22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ22" t="n">
         <v>14</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -4483,37 +4550,37 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E23" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F23" t="n">
         <v>14</v>
       </c>
       <c r="G23" t="n">
-        <v>0.745</v>
+        <v>0.741</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J23" t="n">
         <v>78.2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L23" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="M23" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.397</v>
+        <v>0.394</v>
       </c>
       <c r="O23" t="n">
         <v>19.8</v>
@@ -4522,25 +4589,25 @@
         <v>27.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.72</v>
+        <v>0.719</v>
       </c>
       <c r="R23" t="n">
         <v>10.1</v>
       </c>
       <c r="S23" t="n">
-        <v>33.3</v>
+        <v>33.1</v>
       </c>
       <c r="T23" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="U23" t="n">
         <v>19.3</v>
       </c>
       <c r="V23" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W23" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X23" t="n">
         <v>5.4</v>
@@ -4555,13 +4622,13 @@
         <v>22.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>102.2</v>
+        <v>101.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4576,7 +4643,7 @@
         <v>23</v>
       </c>
       <c r="AI23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ23" t="n">
         <v>26</v>
@@ -4585,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="AL23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM23" t="n">
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO23" t="n">
         <v>10</v>
@@ -4603,13 +4670,13 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AS23" t="n">
         <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU23" t="n">
         <v>29</v>
@@ -4618,10 +4685,10 @@
         <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AX23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY23" t="n">
         <v>3</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -4743,16 +4810,16 @@
         <v>0.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AE24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF24" t="n">
         <v>16</v>
       </c>
-      <c r="AF24" t="n">
-        <v>15</v>
-      </c>
       <c r="AG24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH24" t="n">
         <v>27</v>
@@ -4782,19 +4849,19 @@
         <v>13</v>
       </c>
       <c r="AQ24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR24" t="n">
         <v>2</v>
       </c>
       <c r="AS24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT24" t="n">
         <v>9</v>
       </c>
       <c r="AU24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV24" t="n">
         <v>20</v>
@@ -4809,7 +4876,7 @@
         <v>16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
         <v>12</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -4847,25 +4914,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E25" t="n">
         <v>31</v>
       </c>
       <c r="F25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.574</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="J25" t="n">
-        <v>79.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="K25" t="n">
         <v>0.501</v>
@@ -4877,34 +4944,34 @@
         <v>16.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0.386</v>
+        <v>0.385</v>
       </c>
       <c r="O25" t="n">
         <v>20.9</v>
       </c>
       <c r="P25" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.76</v>
+        <v>0.762</v>
       </c>
       <c r="R25" t="n">
         <v>10.1</v>
       </c>
       <c r="S25" t="n">
-        <v>31.6</v>
+        <v>31.9</v>
       </c>
       <c r="T25" t="n">
-        <v>41.7</v>
+        <v>42</v>
       </c>
       <c r="U25" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="V25" t="n">
         <v>16.1</v>
       </c>
       <c r="W25" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X25" t="n">
         <v>4.8</v>
@@ -4913,7 +4980,7 @@
         <v>4.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA25" t="n">
         <v>22.7</v>
@@ -4922,16 +4989,16 @@
         <v>106.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
       </c>
       <c r="AF25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG25" t="n">
         <v>13</v>
@@ -4949,31 +5016,31 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM25" t="n">
         <v>19</v>
       </c>
       <c r="AN25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO25" t="n">
         <v>4</v>
       </c>
       <c r="AP25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR25" t="n">
         <v>24</v>
       </c>
       <c r="AS25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AT25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AU25" t="n">
         <v>4</v>
@@ -4991,7 +5058,7 @@
         <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA25" t="n">
         <v>7</v>
@@ -5000,7 +5067,7 @@
         <v>3</v>
       </c>
       <c r="BC25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -5032,25 +5099,25 @@
         <v>54</v>
       </c>
       <c r="E26" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G26" t="n">
-        <v>0.648</v>
+        <v>0.63</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.9</v>
+        <v>36.5</v>
       </c>
       <c r="J26" t="n">
-        <v>79.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="K26" t="n">
-        <v>0.466</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
         <v>7.3</v>
@@ -5059,7 +5126,7 @@
         <v>19.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.382</v>
+        <v>0.383</v>
       </c>
       <c r="O26" t="n">
         <v>18.6</v>
@@ -5071,16 +5138,16 @@
         <v>0.762</v>
       </c>
       <c r="R26" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="S26" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="T26" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="U26" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="V26" t="n">
         <v>13.1</v>
@@ -5089,46 +5156,46 @@
         <v>6.9</v>
       </c>
       <c r="X26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="n">
         <v>21.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.7</v>
+        <v>99</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG26" t="n">
         <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ26" t="n">
         <v>20</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL26" t="n">
         <v>10</v>
@@ -5137,34 +5204,34 @@
         <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>19</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>18</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
       </c>
       <c r="AS26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AV26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW26" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AX26" t="n">
         <v>14</v>
@@ -5173,13 +5240,13 @@
         <v>2</v>
       </c>
       <c r="AZ26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA26" t="n">
         <v>13</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-9.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5310,7 +5377,7 @@
         <v>12</v>
       </c>
       <c r="AK27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL27" t="n">
         <v>15</v>
@@ -5322,7 +5389,7 @@
         <v>21</v>
       </c>
       <c r="AO27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP27" t="n">
         <v>12</v>
@@ -5343,7 +5410,7 @@
         <v>25</v>
       </c>
       <c r="AV27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW27" t="n">
         <v>24</v>
@@ -5352,7 +5419,7 @@
         <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ27" t="n">
         <v>28</v>
@@ -5361,7 +5428,7 @@
         <v>10</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>3.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5486,22 +5553,22 @@
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ28" t="n">
         <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM28" t="n">
         <v>8</v>
       </c>
       <c r="AN28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5516,10 +5583,10 @@
         <v>29</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU28" t="n">
         <v>7</v>
@@ -5546,7 +5613,7 @@
         <v>21</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -5575,40 +5642,40 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F29" t="n">
         <v>36</v>
       </c>
       <c r="G29" t="n">
-        <v>0.379</v>
+        <v>0.368</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>36.1</v>
+        <v>35.9</v>
       </c>
       <c r="J29" t="n">
-        <v>79</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L29" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M29" t="n">
         <v>16.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0.374</v>
+        <v>0.371</v>
       </c>
       <c r="O29" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P29" t="n">
         <v>22.6</v>
@@ -5620,13 +5687,13 @@
         <v>8.699999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="T29" t="n">
-        <v>39.2</v>
+        <v>39</v>
       </c>
       <c r="U29" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V29" t="n">
         <v>13.1</v>
@@ -5638,25 +5705,25 @@
         <v>4.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z29" t="n">
         <v>19.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>96.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF29" t="n">
         <v>23</v>
@@ -5668,25 +5735,25 @@
         <v>22</v>
       </c>
       <c r="AI29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AJ29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL29" t="n">
         <v>21</v>
       </c>
       <c r="AM29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP29" t="n">
         <v>26</v>
@@ -5701,19 +5768,19 @@
         <v>13</v>
       </c>
       <c r="AT29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU29" t="n">
         <v>11</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW29" t="n">
         <v>29</v>
       </c>
       <c r="AX29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY29" t="n">
         <v>9</v>
@@ -5722,13 +5789,13 @@
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB29" t="n">
         <v>22</v>
       </c>
       <c r="BC29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5923,7 @@
         <v>18</v>
       </c>
       <c r="AK30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL30" t="n">
         <v>26</v>
@@ -5874,7 +5941,7 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR30" t="n">
         <v>10</v>
@@ -5883,7 +5950,7 @@
         <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
@@ -5895,7 +5962,7 @@
         <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY30" t="n">
         <v>15</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
@@ -6023,10 +6090,10 @@
         <v>27</v>
       </c>
       <c r="AF31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH31" t="n">
         <v>30</v>
@@ -6053,7 +6120,7 @@
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ31" t="n">
         <v>20</v>
@@ -6062,7 +6129,7 @@
         <v>8</v>
       </c>
       <c r="AS31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT31" t="n">
         <v>24</v>
@@ -6080,10 +6147,10 @@
         <v>26</v>
       </c>
       <c r="AY31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-22-2008-09</t>
+          <t>2009-02-22</t>
         </is>
       </c>
     </row>
